--- a/output/pdf_financials_xlsx/CBI.xlsx
+++ b/output/pdf_financials_xlsx/CBI.xlsx
@@ -1682,31 +1682,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.282052</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.052242</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.015524</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.347148</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.309475</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.084095</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.378799</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.016346</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.295061</v>
       </c>
     </row>
     <row r="35">
@@ -1750,31 +1750,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.282052</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.052242</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.015524</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.347148</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.309475</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.084095</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.378799</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.016346</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.295061</v>
       </c>
     </row>
     <row r="37">
@@ -2158,31 +2158,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.295336</v>
+        <v>0.013284</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.315682</v>
+        <v>0.26344</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.100042</v>
+        <v>0.084518</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.707274</v>
+        <v>0.360126</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.301262</v>
+        <v>0.991787</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.833024</v>
+        <v>0.748929</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.8938390000000001</v>
+        <v>0.5150400000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.073669</v>
+        <v>0.057323</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.451207</v>
+        <v>0.156146</v>
       </c>
     </row>
     <row r="49">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -33713,7 +33713,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">

--- a/output/pdf_financials_xlsx/CBI.xlsx
+++ b/output/pdf_financials_xlsx/CBI.xlsx
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003485</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.075</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -4509,19 +4509,19 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>-0.12186</v>
+        <v>1.263105</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0.122518</v>
+        <v>0.828273</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0.019141</v>
+        <v>0.66751</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0.028623</v>
+        <v>0.181377</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="116">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003485</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.281779</v>
+        <v>-0.285264</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.883598</v>
@@ -14857,7 +14857,11 @@
           <t>Proceeds from sale of investments (Note 6)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -16875,7 +16879,11 @@
           <t>Acquisition of investment (Note 6)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -18030,7 +18038,11 @@
           <t>Acquisition of investment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -18091,7 +18103,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -22757,7 +22773,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -28284,7 +28304,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -30912,7 +30936,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E429" s="5" t="n">
         <v>-0.003485</v>
       </c>
